--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ153"/>
+  <dimension ref="A1:AZ154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1243,7 +1243,7 @@
         <v>137297079</v>
       </c>
       <c r="B7" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137296824</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137297076</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137296856</v>
       </c>
       <c r="B19" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137296859</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137296853</v>
       </c>
       <c r="B21" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137296854</v>
       </c>
       <c r="B22" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137296828</v>
       </c>
       <c r="B23" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,32 +3162,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135187635</v>
+        <v>137296825</v>
       </c>
       <c r="B24" t="n">
-        <v>93345</v>
+        <v>92555</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548512</v>
+        <v>548433</v>
       </c>
       <c r="R24" t="n">
-        <v>6941925</v>
+        <v>6941539</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,6 +3251,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3268,13 +3269,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187635</t>
+          <t>https://artportalen.se/Sighting/137296825</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135187640</v>
+        <v>135187635</v>
       </c>
       <c r="B25" t="n">
         <v>93345</v>
@@ -3309,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548533</v>
+        <v>548512</v>
       </c>
       <c r="R25" t="n">
-        <v>6941875</v>
+        <v>6941925</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3344,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3354,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3380,13 +3381,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187640</t>
+          <t>https://artportalen.se/Sighting/135187635</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135187643</v>
+        <v>135187640</v>
       </c>
       <c r="B26" t="n">
         <v>93345</v>
@@ -3421,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548534</v>
+        <v>548533</v>
       </c>
       <c r="R26" t="n">
-        <v>6941755</v>
+        <v>6941875</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3456,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3466,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3492,16 +3493,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187643</t>
+          <t>https://artportalen.se/Sighting/135187640</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137296847</v>
+        <v>135187643</v>
       </c>
       <c r="B27" t="n">
-        <v>93455</v>
+        <v>93345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548533</v>
+        <v>548534</v>
       </c>
       <c r="R27" t="n">
-        <v>6941863</v>
+        <v>6941755</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3563,22 +3564,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,16 +3605,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296847</t>
+          <t>https://artportalen.se/Sighting/135187643</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137296858</v>
+        <v>137296847</v>
       </c>
       <c r="B28" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3645,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548460</v>
+        <v>548533</v>
       </c>
       <c r="R28" t="n">
-        <v>6941803</v>
+        <v>6941863</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3680,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3690,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,16 +3717,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296858</t>
+          <t>https://artportalen.se/Sighting/137296847</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137297071</v>
+        <v>137296858</v>
       </c>
       <c r="B29" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3750,26 +3751,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548443</v>
+        <v>548460</v>
       </c>
       <c r="R29" t="n">
-        <v>6941711</v>
+        <v>6941803</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3801,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3811,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3837,16 +3829,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297071</t>
+          <t>https://artportalen.se/Sighting/137296858</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137297074</v>
+        <v>137297071</v>
       </c>
       <c r="B30" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3865,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3882,10 +3879,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548525</v>
+        <v>548443</v>
       </c>
       <c r="R30" t="n">
-        <v>6941791</v>
+        <v>6941711</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3917,7 +3914,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3927,7 +3924,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3953,16 +3950,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297074</t>
+          <t>https://artportalen.se/Sighting/137297071</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137297084</v>
+        <v>137297074</v>
       </c>
       <c r="B31" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,7 +3986,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3998,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548514</v>
+        <v>548525</v>
       </c>
       <c r="R31" t="n">
-        <v>6941960</v>
+        <v>6941791</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4033,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4069,16 +4066,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297084</t>
+          <t>https://artportalen.se/Sighting/137297074</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137297087</v>
+        <v>137297084</v>
       </c>
       <c r="B32" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4105,7 +4102,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4114,10 +4111,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548527</v>
+        <v>548514</v>
       </c>
       <c r="R32" t="n">
-        <v>6941904</v>
+        <v>6941960</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4149,7 +4146,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4159,7 +4156,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,16 +4182,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297087</t>
+          <t>https://artportalen.se/Sighting/137297084</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137297088</v>
+        <v>137297087</v>
       </c>
       <c r="B33" t="n">
-        <v>93467</v>
+        <v>93456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4202,26 +4199,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4230,10 +4227,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548480</v>
+        <v>548527</v>
       </c>
       <c r="R33" t="n">
-        <v>6941743</v>
+        <v>6941904</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4265,7 +4262,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4275,7 +4272,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4301,54 +4298,58 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297088</t>
+          <t>https://artportalen.se/Sighting/137297087</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135187591</v>
+        <v>137297088</v>
       </c>
       <c r="B34" t="n">
-        <v>92011</v>
+        <v>93468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548481</v>
+        <v>548480</v>
       </c>
       <c r="R34" t="n">
-        <v>6942291</v>
+        <v>6941743</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4372,22 +4373,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4413,38 +4414,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187591</t>
+          <t>https://artportalen.se/Sighting/137297088</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135187586</v>
+        <v>135187591</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>92011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4454,13 +4455,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548453</v>
+        <v>548481</v>
       </c>
       <c r="R35" t="n">
-        <v>6942289</v>
+        <v>6942291</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4489,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4499,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4525,13 +4526,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187586</t>
+          <t>https://artportalen.se/Sighting/135187591</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135187590</v>
+        <v>135187586</v>
       </c>
       <c r="B36" t="n">
         <v>79441</v>
@@ -4566,13 +4567,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548481</v>
+        <v>548453</v>
       </c>
       <c r="R36" t="n">
-        <v>6942295</v>
+        <v>6942289</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4601,7 +4602,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4611,7 +4612,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4637,13 +4638,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187590</t>
+          <t>https://artportalen.se/Sighting/135187586</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135187592</v>
+        <v>135187590</v>
       </c>
       <c r="B37" t="n">
         <v>79441</v>
@@ -4681,10 +4682,10 @@
         <v>548481</v>
       </c>
       <c r="R37" t="n">
-        <v>6942271</v>
+        <v>6942295</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4713,7 +4714,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4723,7 +4724,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4749,13 +4750,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187592</t>
+          <t>https://artportalen.se/Sighting/135187590</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135187600</v>
+        <v>135187592</v>
       </c>
       <c r="B38" t="n">
         <v>79441</v>
@@ -4790,13 +4791,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548479</v>
+        <v>548481</v>
       </c>
       <c r="R38" t="n">
-        <v>6942162</v>
+        <v>6942271</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4825,7 +4826,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4835,7 +4836,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4861,13 +4862,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187600</t>
+          <t>https://artportalen.se/Sighting/135187592</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135187605</v>
+        <v>135187600</v>
       </c>
       <c r="B39" t="n">
         <v>79441</v>
@@ -4902,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548493</v>
+        <v>548479</v>
       </c>
       <c r="R39" t="n">
-        <v>6942119</v>
+        <v>6942162</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4937,7 +4938,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4947,7 +4948,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4973,13 +4974,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187605</t>
+          <t>https://artportalen.se/Sighting/135187600</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135187628</v>
+        <v>135187605</v>
       </c>
       <c r="B40" t="n">
         <v>79441</v>
@@ -5014,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548532</v>
+        <v>548493</v>
       </c>
       <c r="R40" t="n">
-        <v>6941974</v>
+        <v>6942119</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5049,7 +5050,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5059,7 +5060,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5085,13 +5086,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187628</t>
+          <t>https://artportalen.se/Sighting/135187605</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135187630</v>
+        <v>135187628</v>
       </c>
       <c r="B41" t="n">
         <v>79441</v>
@@ -5129,7 +5130,7 @@
         <v>548532</v>
       </c>
       <c r="R41" t="n">
-        <v>6941963</v>
+        <v>6941974</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5161,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5171,7 +5172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5197,13 +5198,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187630</t>
+          <t>https://artportalen.se/Sighting/135187628</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135187632</v>
+        <v>135187630</v>
       </c>
       <c r="B42" t="n">
         <v>79441</v>
@@ -5238,10 +5239,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548496</v>
+        <v>548532</v>
       </c>
       <c r="R42" t="n">
-        <v>6941949</v>
+        <v>6941963</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5273,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5283,7 +5284,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5309,13 +5310,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187632</t>
+          <t>https://artportalen.se/Sighting/135187630</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135187633</v>
+        <v>135187632</v>
       </c>
       <c r="B43" t="n">
         <v>79441</v>
@@ -5350,10 +5351,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548511</v>
+        <v>548496</v>
       </c>
       <c r="R43" t="n">
-        <v>6941930</v>
+        <v>6941949</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5385,7 +5386,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5395,7 +5396,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5421,13 +5422,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187633</t>
+          <t>https://artportalen.se/Sighting/135187632</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135187638</v>
+        <v>135187633</v>
       </c>
       <c r="B44" t="n">
         <v>79441</v>
@@ -5462,10 +5463,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548533</v>
+        <v>548511</v>
       </c>
       <c r="R44" t="n">
-        <v>6941875</v>
+        <v>6941930</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5497,7 +5498,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5507,7 +5508,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5533,13 +5534,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187638</t>
+          <t>https://artportalen.se/Sighting/135187633</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135187644</v>
+        <v>135187638</v>
       </c>
       <c r="B45" t="n">
         <v>79441</v>
@@ -5577,7 +5578,7 @@
         <v>548533</v>
       </c>
       <c r="R45" t="n">
-        <v>6941749</v>
+        <v>6941875</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5609,7 +5610,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5619,7 +5620,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5645,13 +5646,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187644</t>
+          <t>https://artportalen.se/Sighting/135187638</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135187650</v>
+        <v>135187644</v>
       </c>
       <c r="B46" t="n">
         <v>79441</v>
@@ -5686,10 +5687,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548473</v>
+        <v>548533</v>
       </c>
       <c r="R46" t="n">
-        <v>6941664</v>
+        <v>6941749</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5721,7 +5722,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5731,7 +5732,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5757,13 +5758,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187650</t>
+          <t>https://artportalen.se/Sighting/135187644</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135187651</v>
+        <v>135187650</v>
       </c>
       <c r="B47" t="n">
         <v>79441</v>
@@ -5798,10 +5799,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548480</v>
+        <v>548473</v>
       </c>
       <c r="R47" t="n">
-        <v>6941659</v>
+        <v>6941664</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5869,13 +5870,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187651</t>
+          <t>https://artportalen.se/Sighting/135187650</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135187659</v>
+        <v>135187651</v>
       </c>
       <c r="B48" t="n">
         <v>79441</v>
@@ -5910,10 +5911,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548482</v>
+        <v>548480</v>
       </c>
       <c r="R48" t="n">
-        <v>6941521</v>
+        <v>6941659</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5945,7 +5946,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5955,7 +5956,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5981,13 +5982,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187659</t>
+          <t>https://artportalen.se/Sighting/135187651</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135187661</v>
+        <v>135187659</v>
       </c>
       <c r="B49" t="n">
         <v>79441</v>
@@ -6022,10 +6023,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548508</v>
+        <v>548482</v>
       </c>
       <c r="R49" t="n">
-        <v>6941500</v>
+        <v>6941521</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6057,7 +6058,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6067,7 +6068,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6093,13 +6094,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187661</t>
+          <t>https://artportalen.se/Sighting/135187659</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135187663</v>
+        <v>135187661</v>
       </c>
       <c r="B50" t="n">
         <v>79441</v>
@@ -6134,10 +6135,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548496</v>
+        <v>548508</v>
       </c>
       <c r="R50" t="n">
-        <v>6941479</v>
+        <v>6941500</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6169,7 +6170,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6179,7 +6180,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6205,13 +6206,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187663</t>
+          <t>https://artportalen.se/Sighting/135187661</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135187664</v>
+        <v>135187663</v>
       </c>
       <c r="B51" t="n">
         <v>79441</v>
@@ -6246,10 +6247,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548481</v>
+        <v>548496</v>
       </c>
       <c r="R51" t="n">
-        <v>6941488</v>
+        <v>6941479</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6281,7 +6282,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6291,7 +6292,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6317,13 +6318,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187664</t>
+          <t>https://artportalen.se/Sighting/135187663</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135187672</v>
+        <v>135187664</v>
       </c>
       <c r="B52" t="n">
         <v>79441</v>
@@ -6358,10 +6359,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548457</v>
+        <v>548481</v>
       </c>
       <c r="R52" t="n">
-        <v>6941741</v>
+        <v>6941488</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6393,7 +6394,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6403,7 +6404,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6429,13 +6430,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187672</t>
+          <t>https://artportalen.se/Sighting/135187664</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135187675</v>
+        <v>135187672</v>
       </c>
       <c r="B53" t="n">
         <v>79441</v>
@@ -6470,10 +6471,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548479</v>
+        <v>548457</v>
       </c>
       <c r="R53" t="n">
-        <v>6941800</v>
+        <v>6941741</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6505,7 +6506,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6515,7 +6516,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6541,13 +6542,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187675</t>
+          <t>https://artportalen.se/Sighting/135187672</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135187679</v>
+        <v>135187675</v>
       </c>
       <c r="B54" t="n">
         <v>79441</v>
@@ -6582,10 +6583,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548448</v>
+        <v>548479</v>
       </c>
       <c r="R54" t="n">
-        <v>6941934</v>
+        <v>6941800</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6617,7 +6618,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6627,7 +6628,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,16 +6654,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187679</t>
+          <t>https://artportalen.se/Sighting/135187675</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137296820</v>
+        <v>135187679</v>
       </c>
       <c r="B55" t="n">
-        <v>79513</v>
+        <v>79441</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6694,10 +6695,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548477</v>
+        <v>548448</v>
       </c>
       <c r="R55" t="n">
-        <v>6941484</v>
+        <v>6941934</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6724,22 +6725,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6765,13 +6766,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296820</t>
+          <t>https://artportalen.se/Sighting/135187679</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137296823</v>
+        <v>137296820</v>
       </c>
       <c r="B56" t="n">
         <v>79513</v>
@@ -6806,10 +6807,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548473</v>
+        <v>548477</v>
       </c>
       <c r="R56" t="n">
-        <v>6941523</v>
+        <v>6941484</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6841,7 +6842,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6851,7 +6852,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6877,13 +6878,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296823</t>
+          <t>https://artportalen.se/Sighting/137296820</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137296829</v>
+        <v>137296823</v>
       </c>
       <c r="B57" t="n">
         <v>79513</v>
@@ -6918,10 +6919,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548438</v>
+        <v>548473</v>
       </c>
       <c r="R57" t="n">
-        <v>6941576</v>
+        <v>6941523</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6953,7 +6954,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6963,7 +6964,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6989,13 +6990,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296829</t>
+          <t>https://artportalen.se/Sighting/137296823</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137296835</v>
+        <v>137296829</v>
       </c>
       <c r="B58" t="n">
         <v>79513</v>
@@ -7030,10 +7031,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548444</v>
+        <v>548438</v>
       </c>
       <c r="R58" t="n">
-        <v>6941640</v>
+        <v>6941576</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7065,7 +7066,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7075,7 +7076,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7101,13 +7102,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296835</t>
+          <t>https://artportalen.se/Sighting/137296829</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137296843</v>
+        <v>137296835</v>
       </c>
       <c r="B59" t="n">
         <v>79513</v>
@@ -7142,10 +7143,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548534</v>
+        <v>548444</v>
       </c>
       <c r="R59" t="n">
-        <v>6941737</v>
+        <v>6941640</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7177,7 +7178,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7187,7 +7188,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7213,13 +7214,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296843</t>
+          <t>https://artportalen.se/Sighting/137296835</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137296846</v>
+        <v>137296843</v>
       </c>
       <c r="B60" t="n">
         <v>79513</v>
@@ -7254,10 +7255,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548516</v>
+        <v>548534</v>
       </c>
       <c r="R60" t="n">
-        <v>6941859</v>
+        <v>6941737</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7289,7 +7290,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7299,7 +7300,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7325,13 +7326,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296846</t>
+          <t>https://artportalen.se/Sighting/137296843</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137296852</v>
+        <v>137296846</v>
       </c>
       <c r="B61" t="n">
         <v>79513</v>
@@ -7366,10 +7367,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548520</v>
+        <v>548516</v>
       </c>
       <c r="R61" t="n">
-        <v>6941906</v>
+        <v>6941859</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7401,7 +7402,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7411,7 +7412,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7437,13 +7438,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296852</t>
+          <t>https://artportalen.se/Sighting/137296846</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137297060</v>
+        <v>137296852</v>
       </c>
       <c r="B62" t="n">
         <v>79513</v>
@@ -7478,10 +7479,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548440</v>
+        <v>548520</v>
       </c>
       <c r="R62" t="n">
-        <v>6941563</v>
+        <v>6941906</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7513,7 +7514,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7523,7 +7524,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7549,13 +7550,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297060</t>
+          <t>https://artportalen.se/Sighting/137296852</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137297062</v>
+        <v>137297060</v>
       </c>
       <c r="B63" t="n">
         <v>79513</v>
@@ -7590,10 +7591,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548438</v>
+        <v>548440</v>
       </c>
       <c r="R63" t="n">
-        <v>6941577</v>
+        <v>6941563</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7625,7 +7626,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7635,7 +7636,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7661,13 +7662,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297062</t>
+          <t>https://artportalen.se/Sighting/137297060</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137297064</v>
+        <v>137297062</v>
       </c>
       <c r="B64" t="n">
         <v>79513</v>
@@ -7702,10 +7703,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548448</v>
+        <v>548438</v>
       </c>
       <c r="R64" t="n">
-        <v>6941596</v>
+        <v>6941577</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7737,7 +7738,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7747,7 +7748,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7773,13 +7774,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297064</t>
+          <t>https://artportalen.se/Sighting/137297062</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137297069</v>
+        <v>137297064</v>
       </c>
       <c r="B65" t="n">
         <v>79513</v>
@@ -7814,10 +7815,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548450</v>
+        <v>548448</v>
       </c>
       <c r="R65" t="n">
-        <v>6941628</v>
+        <v>6941596</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7849,7 +7850,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7859,7 +7860,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7885,13 +7886,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297069</t>
+          <t>https://artportalen.se/Sighting/137297064</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137297072</v>
+        <v>137297069</v>
       </c>
       <c r="B66" t="n">
         <v>79513</v>
@@ -7926,10 +7927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548437</v>
+        <v>548450</v>
       </c>
       <c r="R66" t="n">
-        <v>6941716</v>
+        <v>6941628</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7961,7 +7962,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7971,7 +7972,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7997,13 +7998,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297072</t>
+          <t>https://artportalen.se/Sighting/137297069</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>137297082</v>
+        <v>137297072</v>
       </c>
       <c r="B67" t="n">
         <v>79513</v>
@@ -8038,10 +8039,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548508</v>
+        <v>548437</v>
       </c>
       <c r="R67" t="n">
-        <v>6941967</v>
+        <v>6941716</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8073,7 +8074,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8083,7 +8084,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8109,38 +8110,38 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297082</t>
+          <t>https://artportalen.se/Sighting/137297072</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137297058</v>
+        <v>137297082</v>
       </c>
       <c r="B68" t="n">
-        <v>79537</v>
+        <v>79513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8150,10 +8151,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548433</v>
+        <v>548508</v>
       </c>
       <c r="R68" t="n">
-        <v>6941501</v>
+        <v>6941967</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8185,7 +8186,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8195,7 +8196,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8221,16 +8222,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297058</t>
+          <t>https://artportalen.se/Sighting/137297082</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137296832</v>
+        <v>137297058</v>
       </c>
       <c r="B69" t="n">
-        <v>83487</v>
+        <v>79537</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8238,21 +8239,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6439</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8262,10 +8263,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548431</v>
+        <v>548433</v>
       </c>
       <c r="R69" t="n">
-        <v>6941585</v>
+        <v>6941501</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8297,7 +8298,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8307,7 +8308,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8333,38 +8334,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296832</t>
+          <t>https://artportalen.se/Sighting/137297058</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135187589</v>
+        <v>137296832</v>
       </c>
       <c r="B70" t="n">
-        <v>83428</v>
+        <v>83487</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8374,13 +8375,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548485</v>
+        <v>548431</v>
       </c>
       <c r="R70" t="n">
-        <v>6942302</v>
+        <v>6941585</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8404,22 +8405,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8445,13 +8446,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187589</t>
+          <t>https://artportalen.se/Sighting/137296832</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135187629</v>
+        <v>135187589</v>
       </c>
       <c r="B71" t="n">
         <v>83428</v>
@@ -8486,13 +8487,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548530</v>
+        <v>548485</v>
       </c>
       <c r="R71" t="n">
-        <v>6941965</v>
+        <v>6942302</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8521,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8531,7 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8557,16 +8558,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187629</t>
+          <t>https://artportalen.se/Sighting/135187589</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137296822</v>
+        <v>135187629</v>
       </c>
       <c r="B72" t="n">
-        <v>83504</v>
+        <v>83428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8598,10 +8599,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548474</v>
+        <v>548530</v>
       </c>
       <c r="R72" t="n">
-        <v>6941523</v>
+        <v>6941965</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8628,22 +8629,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8669,16 +8670,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296822</t>
+          <t>https://artportalen.se/Sighting/135187629</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135187616</v>
+        <v>137296822</v>
       </c>
       <c r="B73" t="n">
-        <v>79198</v>
+        <v>83504</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8686,21 +8687,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8710,10 +8711,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548518</v>
+        <v>548474</v>
       </c>
       <c r="R73" t="n">
-        <v>6942019</v>
+        <v>6941523</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8740,22 +8741,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8781,13 +8782,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187616</t>
+          <t>https://artportalen.se/Sighting/137296822</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135187641</v>
+        <v>135187616</v>
       </c>
       <c r="B74" t="n">
         <v>79198</v>
@@ -8822,10 +8823,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548476</v>
+        <v>548518</v>
       </c>
       <c r="R74" t="n">
-        <v>6941843</v>
+        <v>6942019</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8857,7 +8858,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8867,7 +8868,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8893,16 +8894,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187641</t>
+          <t>https://artportalen.se/Sighting/135187616</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>137296830</v>
+        <v>135187641</v>
       </c>
       <c r="B75" t="n">
-        <v>79270</v>
+        <v>79198</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8934,10 +8935,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548435</v>
+        <v>548476</v>
       </c>
       <c r="R75" t="n">
-        <v>6941585</v>
+        <v>6941843</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8964,22 +8965,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9005,13 +9006,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296830</t>
+          <t>https://artportalen.se/Sighting/135187641</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>137296839</v>
+        <v>137296830</v>
       </c>
       <c r="B76" t="n">
         <v>79270</v>
@@ -9046,13 +9047,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548442</v>
+        <v>548435</v>
       </c>
       <c r="R76" t="n">
-        <v>6941676</v>
+        <v>6941585</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9081,7 +9082,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9091,7 +9092,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9117,13 +9118,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296839</t>
+          <t>https://artportalen.se/Sighting/137296830</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137296844</v>
+        <v>137296839</v>
       </c>
       <c r="B77" t="n">
         <v>79270</v>
@@ -9158,13 +9159,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548534</v>
+        <v>548442</v>
       </c>
       <c r="R77" t="n">
-        <v>6941786</v>
+        <v>6941676</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9193,7 +9194,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9203,7 +9204,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9229,13 +9230,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296844</t>
+          <t>https://artportalen.se/Sighting/137296839</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137296855</v>
+        <v>137296844</v>
       </c>
       <c r="B78" t="n">
         <v>79270</v>
@@ -9270,10 +9271,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548502</v>
+        <v>548534</v>
       </c>
       <c r="R78" t="n">
-        <v>6941977</v>
+        <v>6941786</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9305,7 +9306,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9315,7 +9316,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9341,13 +9342,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296855</t>
+          <t>https://artportalen.se/Sighting/137296844</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137297066</v>
+        <v>137296855</v>
       </c>
       <c r="B79" t="n">
         <v>79270</v>
@@ -9382,10 +9383,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548428</v>
+        <v>548502</v>
       </c>
       <c r="R79" t="n">
-        <v>6941620</v>
+        <v>6941977</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9417,7 +9418,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9427,7 +9428,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9453,16 +9454,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297066</t>
+          <t>https://artportalen.se/Sighting/137296855</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135187613</v>
+        <v>137297066</v>
       </c>
       <c r="B80" t="n">
-        <v>80060</v>
+        <v>79270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9470,21 +9471,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9494,10 +9495,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548529</v>
+        <v>548428</v>
       </c>
       <c r="R80" t="n">
-        <v>6942016</v>
+        <v>6941620</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9524,22 +9525,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9565,13 +9566,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187613</t>
+          <t>https://artportalen.se/Sighting/137297066</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135187615</v>
+        <v>135187613</v>
       </c>
       <c r="B81" t="n">
         <v>80060</v>
@@ -9606,10 +9607,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548526</v>
+        <v>548529</v>
       </c>
       <c r="R81" t="n">
-        <v>6942018</v>
+        <v>6942016</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9677,16 +9678,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187615</t>
+          <t>https://artportalen.se/Sighting/135187613</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137296838</v>
+        <v>135187615</v>
       </c>
       <c r="B82" t="n">
-        <v>80132</v>
+        <v>80060</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9718,10 +9719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548445</v>
+        <v>548526</v>
       </c>
       <c r="R82" t="n">
-        <v>6941675</v>
+        <v>6942018</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9748,22 +9749,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9789,16 +9790,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296838</t>
+          <t>https://artportalen.se/Sighting/135187615</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135187606</v>
+        <v>137296838</v>
       </c>
       <c r="B83" t="n">
-        <v>80556</v>
+        <v>80132</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9806,21 +9807,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9830,10 +9831,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548540</v>
+        <v>548445</v>
       </c>
       <c r="R83" t="n">
-        <v>6942045</v>
+        <v>6941675</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9860,22 +9861,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9901,13 +9902,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187606</t>
+          <t>https://artportalen.se/Sighting/137296838</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135187607</v>
+        <v>135187606</v>
       </c>
       <c r="B84" t="n">
         <v>80556</v>
@@ -9942,10 +9943,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548536</v>
+        <v>548540</v>
       </c>
       <c r="R84" t="n">
-        <v>6942030</v>
+        <v>6942045</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9977,7 +9978,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9987,7 +9988,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10013,13 +10014,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187607</t>
+          <t>https://artportalen.se/Sighting/135187606</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135187610</v>
+        <v>135187607</v>
       </c>
       <c r="B85" t="n">
         <v>80556</v>
@@ -10054,10 +10055,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548537</v>
+        <v>548536</v>
       </c>
       <c r="R85" t="n">
-        <v>6942027</v>
+        <v>6942030</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10125,13 +10126,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187610</t>
+          <t>https://artportalen.se/Sighting/135187607</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135187611</v>
+        <v>135187610</v>
       </c>
       <c r="B86" t="n">
         <v>80556</v>
@@ -10166,10 +10167,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548527</v>
+        <v>548537</v>
       </c>
       <c r="R86" t="n">
-        <v>6942026</v>
+        <v>6942027</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10201,7 +10202,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10211,7 +10212,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10237,13 +10238,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187611</t>
+          <t>https://artportalen.se/Sighting/135187610</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135187619</v>
+        <v>135187611</v>
       </c>
       <c r="B87" t="n">
         <v>80556</v>
@@ -10278,10 +10279,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548528</v>
+        <v>548527</v>
       </c>
       <c r="R87" t="n">
-        <v>6942002</v>
+        <v>6942026</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10313,7 +10314,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10323,7 +10324,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10349,13 +10350,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187619</t>
+          <t>https://artportalen.se/Sighting/135187611</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135187621</v>
+        <v>135187619</v>
       </c>
       <c r="B88" t="n">
         <v>80556</v>
@@ -10390,10 +10391,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548529</v>
+        <v>548528</v>
       </c>
       <c r="R88" t="n">
-        <v>6941999</v>
+        <v>6942002</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10425,7 +10426,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10435,7 +10436,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10461,13 +10462,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187621</t>
+          <t>https://artportalen.se/Sighting/135187619</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135187622</v>
+        <v>135187621</v>
       </c>
       <c r="B89" t="n">
         <v>80556</v>
@@ -10502,10 +10503,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548530</v>
+        <v>548529</v>
       </c>
       <c r="R89" t="n">
-        <v>6941987</v>
+        <v>6941999</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10537,7 +10538,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10547,7 +10548,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10573,13 +10574,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187622</t>
+          <t>https://artportalen.se/Sighting/135187621</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135187624</v>
+        <v>135187622</v>
       </c>
       <c r="B90" t="n">
         <v>80556</v>
@@ -10614,10 +10615,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548536</v>
+        <v>548530</v>
       </c>
       <c r="R90" t="n">
-        <v>6941982</v>
+        <v>6941987</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10649,7 +10650,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10659,7 +10660,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10685,13 +10686,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187624</t>
+          <t>https://artportalen.se/Sighting/135187622</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135187626</v>
+        <v>135187624</v>
       </c>
       <c r="B91" t="n">
         <v>80556</v>
@@ -10726,10 +10727,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548533</v>
+        <v>548536</v>
       </c>
       <c r="R91" t="n">
-        <v>6941977</v>
+        <v>6941982</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10761,7 +10762,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10771,7 +10772,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10797,13 +10798,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187626</t>
+          <t>https://artportalen.se/Sighting/135187624</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135187647</v>
+        <v>135187626</v>
       </c>
       <c r="B92" t="n">
         <v>80556</v>
@@ -10838,10 +10839,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548479</v>
+        <v>548533</v>
       </c>
       <c r="R92" t="n">
-        <v>6941717</v>
+        <v>6941977</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10873,7 +10874,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10883,7 +10884,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10909,13 +10910,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187647</t>
+          <t>https://artportalen.se/Sighting/135187626</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135187677</v>
+        <v>135187647</v>
       </c>
       <c r="B93" t="n">
         <v>80556</v>
@@ -10950,10 +10951,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548452</v>
+        <v>548479</v>
       </c>
       <c r="R93" t="n">
-        <v>6941854</v>
+        <v>6941717</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10985,7 +10986,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10995,7 +10996,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11021,16 +11022,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187677</t>
+          <t>https://artportalen.se/Sighting/135187647</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>137297056</v>
+        <v>135187677</v>
       </c>
       <c r="B94" t="n">
-        <v>80628</v>
+        <v>80556</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11062,10 +11063,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548457</v>
+        <v>548452</v>
       </c>
       <c r="R94" t="n">
-        <v>6941481</v>
+        <v>6941854</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11092,22 +11093,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11133,38 +11134,38 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297056</t>
+          <t>https://artportalen.se/Sighting/135187677</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135187618</v>
+        <v>137297056</v>
       </c>
       <c r="B95" t="n">
-        <v>80560</v>
+        <v>80628</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11174,10 +11175,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>548512</v>
+        <v>548457</v>
       </c>
       <c r="R95" t="n">
-        <v>6942033</v>
+        <v>6941481</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11204,22 +11205,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11245,16 +11246,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187618</t>
+          <t>https://artportalen.se/Sighting/137297056</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135187596</v>
+        <v>135187618</v>
       </c>
       <c r="B96" t="n">
-        <v>80567</v>
+        <v>80560</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11262,21 +11263,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11286,13 +11287,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>548504</v>
+        <v>548512</v>
       </c>
       <c r="R96" t="n">
-        <v>6942211</v>
+        <v>6942033</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11321,7 +11322,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11331,7 +11332,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11357,13 +11358,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187596</t>
+          <t>https://artportalen.se/Sighting/135187618</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135187598</v>
+        <v>135187596</v>
       </c>
       <c r="B97" t="n">
         <v>80567</v>
@@ -11398,10 +11399,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>548490</v>
+        <v>548504</v>
       </c>
       <c r="R97" t="n">
-        <v>6942192</v>
+        <v>6942211</v>
       </c>
       <c r="S97" t="n">
         <v>6</v>
@@ -11433,7 +11434,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11443,7 +11444,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11469,13 +11470,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187598</t>
+          <t>https://artportalen.se/Sighting/135187596</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135187678</v>
+        <v>135187598</v>
       </c>
       <c r="B98" t="n">
         <v>80567</v>
@@ -11510,13 +11511,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>548443</v>
+        <v>548490</v>
       </c>
       <c r="R98" t="n">
-        <v>6941871</v>
+        <v>6942192</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11545,7 +11546,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11555,7 +11556,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11581,16 +11582,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187678</t>
+          <t>https://artportalen.se/Sighting/135187598</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135187646</v>
+        <v>135187678</v>
       </c>
       <c r="B99" t="n">
-        <v>80568</v>
+        <v>80567</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11598,21 +11599,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11622,10 +11623,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>548480</v>
+        <v>548443</v>
       </c>
       <c r="R99" t="n">
-        <v>6941717</v>
+        <v>6941871</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11657,7 +11658,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11667,7 +11668,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11693,16 +11694,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187646</t>
+          <t>https://artportalen.se/Sighting/135187678</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137296841</v>
+        <v>135187646</v>
       </c>
       <c r="B100" t="n">
-        <v>80640</v>
+        <v>80568</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11734,10 +11735,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>548476</v>
+        <v>548480</v>
       </c>
       <c r="R100" t="n">
-        <v>6941713</v>
+        <v>6941717</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11764,22 +11765,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11805,52 +11806,51 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296841</t>
+          <t>https://artportalen.se/Sighting/135187646</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137296831</v>
+        <v>137296841</v>
       </c>
       <c r="B101" t="n">
-        <v>58033</v>
+        <v>80640</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>548431</v>
+        <v>548476</v>
       </c>
       <c r="R101" t="n">
-        <v>6941585</v>
+        <v>6941713</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11892,12 +11892,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11923,13 +11918,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296831</t>
+          <t>https://artportalen.se/Sighting/137296841</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137296833</v>
+        <v>137296831</v>
       </c>
       <c r="B102" t="n">
         <v>58033</v>
@@ -11965,10 +11960,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>548435</v>
+        <v>548431</v>
       </c>
       <c r="R102" t="n">
-        <v>6941589</v>
+        <v>6941585</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12000,7 +11995,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12010,12 +12005,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12041,13 +12036,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296833</t>
+          <t>https://artportalen.se/Sighting/137296831</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137296836</v>
+        <v>137296833</v>
       </c>
       <c r="B103" t="n">
         <v>58033</v>
@@ -12083,10 +12078,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>548448</v>
+        <v>548435</v>
       </c>
       <c r="R103" t="n">
-        <v>6941655</v>
+        <v>6941589</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12118,7 +12113,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12128,7 +12123,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -12159,13 +12154,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296836</t>
+          <t>https://artportalen.se/Sighting/137296833</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137297075</v>
+        <v>137296836</v>
       </c>
       <c r="B104" t="n">
         <v>58033</v>
@@ -12201,10 +12196,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>548487</v>
+        <v>548448</v>
       </c>
       <c r="R104" t="n">
-        <v>6941801</v>
+        <v>6941655</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12236,7 +12231,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12246,7 +12241,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -12277,13 +12272,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297075</t>
+          <t>https://artportalen.se/Sighting/137296836</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137297085</v>
+        <v>137297075</v>
       </c>
       <c r="B105" t="n">
         <v>58033</v>
@@ -12319,10 +12314,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>548531</v>
+        <v>548487</v>
       </c>
       <c r="R105" t="n">
-        <v>6941923</v>
+        <v>6941801</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12354,7 +12349,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12364,7 +12359,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -12395,13 +12390,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297085</t>
+          <t>https://artportalen.se/Sighting/137297075</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>137297086</v>
+        <v>137297085</v>
       </c>
       <c r="B106" t="n">
         <v>58033</v>
@@ -12437,13 +12432,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>548542</v>
+        <v>548531</v>
       </c>
       <c r="R106" t="n">
-        <v>6941919</v>
+        <v>6941923</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12472,7 +12467,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12482,7 +12477,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -12513,62 +12508,55 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297086</t>
+          <t>https://artportalen.se/Sighting/137297085</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137296842</v>
+        <v>137297086</v>
       </c>
       <c r="B107" t="n">
-        <v>58025</v>
+        <v>58033</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>548489</v>
+        <v>548542</v>
       </c>
       <c r="R107" t="n">
-        <v>6941730</v>
+        <v>6941919</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12597,7 +12585,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12607,12 +12595,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Verkar upprörda över min närvaro.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12638,16 +12626,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296842</t>
+          <t>https://artportalen.se/Sighting/137297086</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135187673</v>
+        <v>137296842</v>
       </c>
       <c r="B108" t="n">
-        <v>57167</v>
+        <v>58025</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12655,31 +12643,31 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>100110</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12687,10 +12675,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>548461</v>
+        <v>548489</v>
       </c>
       <c r="R108" t="n">
-        <v>6941762</v>
+        <v>6941730</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12717,27 +12705,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Fjäder i sandgrop</t>
+          <t>Verkar upprörda över min närvaro.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12763,50 +12751,46 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187673</t>
+          <t>https://artportalen.se/Sighting/137296842</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135187657</v>
+        <v>135187673</v>
       </c>
       <c r="B109" t="n">
-        <v>57801</v>
+        <v>57167</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>102976</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -12816,10 +12800,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>548541</v>
+        <v>548461</v>
       </c>
       <c r="R109" t="n">
-        <v>6941582</v>
+        <v>6941762</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12851,7 +12835,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12861,7 +12845,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Fjäder i sandgrop</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12887,13 +12876,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187657</t>
+          <t>https://artportalen.se/Sighting/135187673</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135187674</v>
+        <v>135187657</v>
       </c>
       <c r="B110" t="n">
         <v>57801</v>
@@ -12921,7 +12910,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
@@ -12936,10 +12929,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>548466</v>
+        <v>548541</v>
       </c>
       <c r="R110" t="n">
-        <v>6941771</v>
+        <v>6941582</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12971,7 +12964,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12981,7 +12974,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13007,45 +13000,41 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187674</t>
+          <t>https://artportalen.se/Sighting/135187657</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135187660</v>
+        <v>135187674</v>
       </c>
       <c r="B111" t="n">
-        <v>58141</v>
+        <v>57801</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>102976</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
@@ -13060,10 +13049,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>548506</v>
+        <v>548466</v>
       </c>
       <c r="R111" t="n">
-        <v>6941500</v>
+        <v>6941771</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13095,7 +13084,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13105,7 +13094,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13131,16 +13120,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187660</t>
+          <t>https://artportalen.se/Sighting/135187674</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137296848</v>
+        <v>135187660</v>
       </c>
       <c r="B112" t="n">
-        <v>58194</v>
+        <v>58141</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13167,20 +13156,27 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>548546</v>
+        <v>548506</v>
       </c>
       <c r="R112" t="n">
-        <v>6941880</v>
+        <v>6941500</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13207,22 +13203,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13248,63 +13244,56 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296848</t>
+          <t>https://artportalen.se/Sighting/135187660</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135187665</v>
+        <v>137296848</v>
       </c>
       <c r="B113" t="n">
-        <v>58136</v>
+        <v>58194</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>548478</v>
+        <v>548546</v>
       </c>
       <c r="R113" t="n">
-        <v>6941492</v>
+        <v>6941880</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13331,22 +13320,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13372,16 +13361,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187665</t>
+          <t>https://artportalen.se/Sighting/137296848</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>137296851</v>
+        <v>135187665</v>
       </c>
       <c r="B114" t="n">
-        <v>58189</v>
+        <v>58136</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13402,11 @@
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -13421,10 +13414,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>548528</v>
+        <v>548478</v>
       </c>
       <c r="R114" t="n">
-        <v>6941892</v>
+        <v>6941492</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13451,22 +13444,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13492,54 +13485,62 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296851</t>
+          <t>https://artportalen.se/Sighting/135187665</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135187595</v>
+        <v>137296851</v>
       </c>
       <c r="B115" t="n">
-        <v>99274</v>
+        <v>58189</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>548483</v>
+        <v>548528</v>
       </c>
       <c r="R115" t="n">
-        <v>6942226</v>
+        <v>6941892</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13563,27 +13564,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>90 ex</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13609,13 +13605,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187595</t>
+          <t>https://artportalen.se/Sighting/137296851</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135187602</v>
+        <v>135187595</v>
       </c>
       <c r="B116" t="n">
         <v>99274</v>
@@ -13650,13 +13646,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>548503</v>
+        <v>548483</v>
       </c>
       <c r="R116" t="n">
-        <v>6942148</v>
+        <v>6942226</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13685,7 +13681,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13695,12 +13691,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>90 ex</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13726,13 +13722,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187602</t>
+          <t>https://artportalen.se/Sighting/135187595</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135187603</v>
+        <v>135187602</v>
       </c>
       <c r="B117" t="n">
         <v>99274</v>
@@ -13767,10 +13763,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>548494</v>
+        <v>548503</v>
       </c>
       <c r="R117" t="n">
-        <v>6942137</v>
+        <v>6942148</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13802,7 +13798,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13812,12 +13808,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13843,13 +13839,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187603</t>
+          <t>https://artportalen.se/Sighting/135187602</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135187623</v>
+        <v>135187603</v>
       </c>
       <c r="B118" t="n">
         <v>99274</v>
@@ -13884,10 +13880,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>548531</v>
+        <v>548494</v>
       </c>
       <c r="R118" t="n">
-        <v>6941985</v>
+        <v>6942137</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13919,7 +13915,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13929,12 +13925,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>26 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13960,13 +13956,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187623</t>
+          <t>https://artportalen.se/Sighting/135187603</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135187645</v>
+        <v>135187623</v>
       </c>
       <c r="B119" t="n">
         <v>99274</v>
@@ -14001,10 +13997,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>548494</v>
+        <v>548531</v>
       </c>
       <c r="R119" t="n">
-        <v>6941712</v>
+        <v>6941985</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -14036,7 +14032,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14046,12 +14042,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>26 ex</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14077,13 +14073,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187645</t>
+          <t>https://artportalen.se/Sighting/135187623</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135187649</v>
+        <v>135187645</v>
       </c>
       <c r="B120" t="n">
         <v>99274</v>
@@ -14118,13 +14114,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>548475</v>
+        <v>548494</v>
       </c>
       <c r="R120" t="n">
-        <v>6941667</v>
+        <v>6941712</v>
       </c>
       <c r="S120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14153,7 +14149,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14163,12 +14159,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14194,13 +14190,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187649</t>
+          <t>https://artportalen.se/Sighting/135187645</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135187654</v>
+        <v>135187649</v>
       </c>
       <c r="B121" t="n">
         <v>99274</v>
@@ -14235,13 +14231,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>548522</v>
+        <v>548475</v>
       </c>
       <c r="R121" t="n">
-        <v>6941614</v>
+        <v>6941667</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14270,7 +14266,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14280,12 +14276,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>12 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14311,13 +14307,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187654</t>
+          <t>https://artportalen.se/Sighting/135187649</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135187655</v>
+        <v>135187654</v>
       </c>
       <c r="B122" t="n">
         <v>99274</v>
@@ -14352,13 +14348,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>548521</v>
+        <v>548522</v>
       </c>
       <c r="R122" t="n">
-        <v>6941608</v>
+        <v>6941614</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14387,7 +14383,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14397,12 +14393,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>12 ex</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14428,13 +14424,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187655</t>
+          <t>https://artportalen.se/Sighting/135187654</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135187658</v>
+        <v>135187655</v>
       </c>
       <c r="B123" t="n">
         <v>99274</v>
@@ -14469,10 +14465,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>548510</v>
+        <v>548521</v>
       </c>
       <c r="R123" t="n">
-        <v>6941570</v>
+        <v>6941608</v>
       </c>
       <c r="S123" t="n">
         <v>6</v>
@@ -14504,7 +14500,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14514,12 +14510,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14545,13 +14541,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187658</t>
+          <t>https://artportalen.se/Sighting/135187655</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135187666</v>
+        <v>135187658</v>
       </c>
       <c r="B124" t="n">
         <v>99274</v>
@@ -14580,20 +14576,16 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>548468</v>
+        <v>548510</v>
       </c>
       <c r="R124" t="n">
-        <v>6941502</v>
+        <v>6941570</v>
       </c>
       <c r="S124" t="n">
         <v>6</v>
@@ -14625,7 +14617,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14635,12 +14627,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14649,7 +14641,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14667,13 +14658,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187666</t>
+          <t>https://artportalen.se/Sighting/135187658</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135187670</v>
+        <v>135187666</v>
       </c>
       <c r="B125" t="n">
         <v>99274</v>
@@ -14702,19 +14693,23 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>548485</v>
+        <v>548468</v>
       </c>
       <c r="R125" t="n">
-        <v>6941626</v>
+        <v>6941502</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14743,7 +14738,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14753,7 +14748,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -14767,6 +14762,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14784,13 +14780,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187670</t>
+          <t>https://artportalen.se/Sighting/135187666</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135187671</v>
+        <v>135187670</v>
       </c>
       <c r="B126" t="n">
         <v>99274</v>
@@ -14825,10 +14821,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>548456</v>
+        <v>548485</v>
       </c>
       <c r="R126" t="n">
-        <v>6941709</v>
+        <v>6941626</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14860,7 +14856,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14870,12 +14866,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14901,16 +14897,16 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187671</t>
+          <t>https://artportalen.se/Sighting/135187670</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>137296821</v>
+        <v>135187671</v>
       </c>
       <c r="B127" t="n">
-        <v>99404</v>
+        <v>99274</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14935,26 +14931,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>548478</v>
+        <v>548456</v>
       </c>
       <c r="R127" t="n">
-        <v>6941485</v>
+        <v>6941709</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14981,22 +14968,27 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15022,16 +15014,16 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296821</t>
+          <t>https://artportalen.se/Sighting/135187671</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>137296826</v>
+        <v>137296821</v>
       </c>
       <c r="B128" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15058,7 +15050,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15072,10 +15064,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>548453</v>
+        <v>548478</v>
       </c>
       <c r="R128" t="n">
-        <v>6941552</v>
+        <v>6941485</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15107,7 +15099,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15117,7 +15109,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15143,16 +15135,16 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296826</t>
+          <t>https://artportalen.se/Sighting/137296821</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>137296827</v>
+        <v>137296826</v>
       </c>
       <c r="B129" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15179,7 +15171,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15193,10 +15185,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>548440</v>
+        <v>548453</v>
       </c>
       <c r="R129" t="n">
-        <v>6941582</v>
+        <v>6941552</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15228,7 +15220,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15238,7 +15230,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15264,16 +15256,16 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296827</t>
+          <t>https://artportalen.se/Sighting/137296826</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>137297059</v>
+        <v>137296827</v>
       </c>
       <c r="B130" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15300,7 +15292,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -15314,13 +15306,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>548439</v>
+        <v>548440</v>
       </c>
       <c r="R130" t="n">
-        <v>6941550</v>
+        <v>6941582</v>
       </c>
       <c r="S130" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15349,7 +15341,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15359,7 +15351,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15385,16 +15377,16 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297059</t>
+          <t>https://artportalen.se/Sighting/137296827</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>137297061</v>
+        <v>137297059</v>
       </c>
       <c r="B131" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15421,7 +15413,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -15435,13 +15427,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>548438</v>
+        <v>548439</v>
       </c>
       <c r="R131" t="n">
-        <v>6941577</v>
+        <v>6941550</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15470,7 +15462,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15480,12 +15472,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Varav 14 har blommat</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15511,16 +15498,16 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297061</t>
+          <t>https://artportalen.se/Sighting/137297059</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>137297063</v>
+        <v>137297061</v>
       </c>
       <c r="B132" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15547,7 +15534,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15561,10 +15548,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>548444</v>
+        <v>548438</v>
       </c>
       <c r="R132" t="n">
-        <v>6941596</v>
+        <v>6941577</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15596,7 +15583,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15606,12 +15593,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>4 har blommat</t>
+          <t>Varav 14 har blommat</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15637,16 +15624,16 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297063</t>
+          <t>https://artportalen.se/Sighting/137297061</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>137297065</v>
+        <v>137297063</v>
       </c>
       <c r="B133" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15673,7 +15660,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15690,7 +15677,7 @@
         <v>548444</v>
       </c>
       <c r="R133" t="n">
-        <v>6941602</v>
+        <v>6941596</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15722,7 +15709,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15732,12 +15719,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>7 har blommat</t>
+          <t>4 har blommat</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15763,16 +15750,16 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297065</t>
+          <t>https://artportalen.se/Sighting/137297063</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>137297067</v>
+        <v>137297065</v>
       </c>
       <c r="B134" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15799,7 +15786,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15813,10 +15800,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>548434</v>
+        <v>548444</v>
       </c>
       <c r="R134" t="n">
-        <v>6941632</v>
+        <v>6941602</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -15848,7 +15835,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15858,7 +15845,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>7 har blommat</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15884,16 +15876,16 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297067</t>
+          <t>https://artportalen.se/Sighting/137297065</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>137297068</v>
+        <v>137297067</v>
       </c>
       <c r="B135" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15920,7 +15912,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15934,7 +15926,7 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>548442</v>
+        <v>548434</v>
       </c>
       <c r="R135" t="n">
         <v>6941632</v>
@@ -15969,7 +15961,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15979,7 +15971,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16005,16 +15997,16 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297068</t>
+          <t>https://artportalen.se/Sighting/137297067</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>137297070</v>
+        <v>137297068</v>
       </c>
       <c r="B136" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16041,7 +16033,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -16055,10 +16047,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>548459</v>
+        <v>548442</v>
       </c>
       <c r="R136" t="n">
-        <v>6941633</v>
+        <v>6941632</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -16090,7 +16082,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16100,7 +16092,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16126,16 +16118,16 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297070</t>
+          <t>https://artportalen.se/Sighting/137297068</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>137297073</v>
+        <v>137297070</v>
       </c>
       <c r="B137" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16162,7 +16154,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -16176,10 +16168,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>548451</v>
+        <v>548459</v>
       </c>
       <c r="R137" t="n">
-        <v>6941715</v>
+        <v>6941633</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16211,7 +16203,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16221,7 +16213,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16247,16 +16239,16 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297073</t>
+          <t>https://artportalen.se/Sighting/137297070</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>137297077</v>
+        <v>137297073</v>
       </c>
       <c r="B138" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16297,13 +16289,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>548470</v>
+        <v>548451</v>
       </c>
       <c r="R138" t="n">
-        <v>6941875</v>
+        <v>6941715</v>
       </c>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16332,7 +16324,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16342,7 +16334,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16368,51 +16360,60 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297077</t>
+          <t>https://artportalen.se/Sighting/137297073</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>137297078</v>
+        <v>137297077</v>
       </c>
       <c r="B139" t="n">
-        <v>98266</v>
+        <v>99405</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Mycksjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>548468</v>
+        <v>548470</v>
       </c>
       <c r="R139" t="n">
-        <v>6941877</v>
+        <v>6941875</v>
       </c>
       <c r="S139" t="n">
         <v>6</v>
@@ -16444,7 +16445,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16454,7 +16455,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16480,38 +16481,38 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297078</t>
+          <t>https://artportalen.se/Sighting/137297077</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135187588</v>
+        <v>137297078</v>
       </c>
       <c r="B140" t="n">
-        <v>79199</v>
+        <v>98267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16521,13 +16522,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>548475</v>
+        <v>548468</v>
       </c>
       <c r="R140" t="n">
-        <v>6942314</v>
+        <v>6941877</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16551,22 +16552,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16592,13 +16593,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187588</t>
+          <t>https://artportalen.se/Sighting/137297078</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135187614</v>
+        <v>135187588</v>
       </c>
       <c r="B141" t="n">
         <v>79199</v>
@@ -16633,10 +16634,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>548529</v>
+        <v>548475</v>
       </c>
       <c r="R141" t="n">
-        <v>6942015</v>
+        <v>6942314</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16668,7 +16669,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16678,7 +16679,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16704,13 +16705,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187614</t>
+          <t>https://artportalen.se/Sighting/135187588</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135187642</v>
+        <v>135187614</v>
       </c>
       <c r="B142" t="n">
         <v>79199</v>
@@ -16745,10 +16746,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>548486</v>
+        <v>548529</v>
       </c>
       <c r="R142" t="n">
-        <v>6941838</v>
+        <v>6942015</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16780,7 +16781,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16790,7 +16791,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16816,13 +16817,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187642</t>
+          <t>https://artportalen.se/Sighting/135187614</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135187676</v>
+        <v>135187642</v>
       </c>
       <c r="B143" t="n">
         <v>79199</v>
@@ -16857,10 +16858,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>548467</v>
+        <v>548486</v>
       </c>
       <c r="R143" t="n">
-        <v>6941834</v>
+        <v>6941838</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -16892,7 +16893,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16902,7 +16903,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16928,16 +16929,16 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187676</t>
+          <t>https://artportalen.se/Sighting/135187642</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>137296837</v>
+        <v>135187676</v>
       </c>
       <c r="B144" t="n">
-        <v>79271</v>
+        <v>79199</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16969,10 +16970,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>548444</v>
+        <v>548467</v>
       </c>
       <c r="R144" t="n">
-        <v>6941675</v>
+        <v>6941834</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -16999,22 +17000,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17040,13 +17041,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296837</t>
+          <t>https://artportalen.se/Sighting/135187676</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>137296840</v>
+        <v>137296837</v>
       </c>
       <c r="B145" t="n">
         <v>79271</v>
@@ -17081,10 +17082,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>548484</v>
+        <v>548444</v>
       </c>
       <c r="R145" t="n">
-        <v>6941713</v>
+        <v>6941675</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -17116,7 +17117,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17126,7 +17127,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17152,13 +17153,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137296840</t>
+          <t>https://artportalen.se/Sighting/137296837</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>137297081</v>
+        <v>137296840</v>
       </c>
       <c r="B146" t="n">
         <v>79271</v>
@@ -17193,10 +17194,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>548482</v>
+        <v>548484</v>
       </c>
       <c r="R146" t="n">
-        <v>6941926</v>
+        <v>6941713</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -17228,7 +17229,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17238,7 +17239,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17264,13 +17265,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297081</t>
+          <t>https://artportalen.se/Sighting/137296840</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>137297083</v>
+        <v>137297081</v>
       </c>
       <c r="B147" t="n">
         <v>79271</v>
@@ -17305,10 +17306,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>548512</v>
+        <v>548482</v>
       </c>
       <c r="R147" t="n">
-        <v>6941959</v>
+        <v>6941926</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -17340,7 +17341,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17350,7 +17351,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17376,38 +17377,38 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137297083</t>
+          <t>https://artportalen.se/Sighting/137297081</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135187593</v>
+        <v>137297083</v>
       </c>
       <c r="B148" t="n">
-        <v>80506</v>
+        <v>79271</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17417,13 +17418,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>548478</v>
+        <v>548512</v>
       </c>
       <c r="R148" t="n">
-        <v>6942236</v>
+        <v>6941959</v>
       </c>
       <c r="S148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17447,22 +17448,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17488,13 +17489,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187593</t>
+          <t>https://artportalen.se/Sighting/137297083</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135187601</v>
+        <v>135187593</v>
       </c>
       <c r="B149" t="n">
         <v>80506</v>
@@ -17529,13 +17530,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>548502</v>
+        <v>548478</v>
       </c>
       <c r="R149" t="n">
-        <v>6942157</v>
+        <v>6942236</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17564,7 +17565,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17574,7 +17575,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17600,13 +17601,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187601</t>
+          <t>https://artportalen.se/Sighting/135187593</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135187608</v>
+        <v>135187601</v>
       </c>
       <c r="B150" t="n">
         <v>80506</v>
@@ -17641,10 +17642,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>548536</v>
+        <v>548502</v>
       </c>
       <c r="R150" t="n">
-        <v>6942028</v>
+        <v>6942157</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17676,7 +17677,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17686,7 +17687,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17712,13 +17713,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187608</t>
+          <t>https://artportalen.se/Sighting/135187601</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135187625</v>
+        <v>135187608</v>
       </c>
       <c r="B151" t="n">
         <v>80506</v>
@@ -17753,10 +17754,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>548535</v>
+        <v>548536</v>
       </c>
       <c r="R151" t="n">
-        <v>6941980</v>
+        <v>6942028</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17788,7 +17789,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17798,7 +17799,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17824,13 +17825,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187625</t>
+          <t>https://artportalen.se/Sighting/135187608</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135187627</v>
+        <v>135187625</v>
       </c>
       <c r="B152" t="n">
         <v>80506</v>
@@ -17865,10 +17866,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>548533</v>
+        <v>548535</v>
       </c>
       <c r="R152" t="n">
-        <v>6941977</v>
+        <v>6941980</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -17900,7 +17901,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17910,7 +17911,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17936,13 +17937,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135187627</t>
+          <t>https://artportalen.se/Sighting/135187625</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135187652</v>
+        <v>135187627</v>
       </c>
       <c r="B153" t="n">
         <v>80506</v>
@@ -17977,10 +17978,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>548493</v>
+        <v>548533</v>
       </c>
       <c r="R153" t="n">
-        <v>6941639</v>
+        <v>6941977</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18012,7 +18013,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18022,7 +18023,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18047,6 +18048,118 @@
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187627</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>135187652</v>
+      </c>
+      <c r="B154" t="n">
+        <v>80506</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Mycksjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>548493</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6941639</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135187652</t>
         </is>
@@ -18206,6 +18319,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>137297079</v>
       </c>
       <c r="B7" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137296849</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137296857</v>
       </c>
       <c r="B12" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137297080</v>
       </c>
       <c r="B13" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137296824</v>
       </c>
       <c r="B16" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137297076</v>
       </c>
       <c r="B17" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137296856</v>
       </c>
       <c r="B19" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137296859</v>
       </c>
       <c r="B20" t="n">
-        <v>92170</v>
+        <v>92173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137296853</v>
       </c>
       <c r="B21" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137296854</v>
       </c>
       <c r="B22" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137296828</v>
       </c>
       <c r="B23" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137296825</v>
       </c>
       <c r="B24" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>137296847</v>
       </c>
       <c r="B28" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>137296858</v>
       </c>
       <c r="B29" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>137297071</v>
       </c>
       <c r="B30" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>137297074</v>
       </c>
       <c r="B31" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137297084</v>
       </c>
       <c r="B32" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>137297087</v>
       </c>
       <c r="B33" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137297088</v>
       </c>
       <c r="B34" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>137296820</v>
       </c>
       <c r="B56" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>137296823</v>
       </c>
       <c r="B57" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>137296829</v>
       </c>
       <c r="B58" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>137296835</v>
       </c>
       <c r="B59" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>137296843</v>
       </c>
       <c r="B60" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>137296846</v>
       </c>
       <c r="B61" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>137296852</v>
       </c>
       <c r="B62" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>137297060</v>
       </c>
       <c r="B63" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>137297062</v>
       </c>
       <c r="B64" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137297064</v>
       </c>
       <c r="B65" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137297069</v>
       </c>
       <c r="B66" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>137297072</v>
       </c>
       <c r="B67" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>137297082</v>
       </c>
       <c r="B68" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>137297058</v>
       </c>
       <c r="B69" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>137296832</v>
       </c>
       <c r="B70" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>137296822</v>
       </c>
       <c r="B73" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>137296830</v>
       </c>
       <c r="B76" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137296839</v>
       </c>
       <c r="B77" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>137296844</v>
       </c>
       <c r="B78" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137296855</v>
       </c>
       <c r="B79" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>137297066</v>
       </c>
       <c r="B80" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>137296838</v>
       </c>
       <c r="B83" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137297056</v>
       </c>
       <c r="B95" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>137296841</v>
       </c>
       <c r="B101" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>137296831</v>
       </c>
       <c r="B102" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>137296833</v>
       </c>
       <c r="B103" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>137296836</v>
       </c>
       <c r="B104" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>137297075</v>
       </c>
       <c r="B105" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>137297085</v>
       </c>
       <c r="B106" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>137297086</v>
       </c>
       <c r="B107" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>137296842</v>
       </c>
       <c r="B108" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>137296848</v>
       </c>
       <c r="B113" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>137296851</v>
       </c>
       <c r="B115" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>137296821</v>
       </c>
       <c r="B128" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>137296826</v>
       </c>
       <c r="B129" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>137296827</v>
       </c>
       <c r="B130" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137297059</v>
       </c>
       <c r="B131" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>137297061</v>
       </c>
       <c r="B132" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>137297063</v>
       </c>
       <c r="B133" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>137297065</v>
       </c>
       <c r="B134" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>137297067</v>
       </c>
       <c r="B135" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137297068</v>
       </c>
       <c r="B136" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137297070</v>
       </c>
       <c r="B137" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>137297073</v>
       </c>
       <c r="B138" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>137297077</v>
       </c>
       <c r="B139" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>137297078</v>
       </c>
       <c r="B140" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>137296837</v>
       </c>
       <c r="B145" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>137296840</v>
       </c>
       <c r="B146" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>137297081</v>
       </c>
       <c r="B147" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>137297083</v>
       </c>
       <c r="B148" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>137297079</v>
       </c>
       <c r="B7" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137296824</v>
       </c>
       <c r="B16" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137297076</v>
       </c>
       <c r="B17" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137296856</v>
       </c>
       <c r="B19" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137296859</v>
       </c>
       <c r="B20" t="n">
-        <v>92173</v>
+        <v>92175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137296853</v>
       </c>
       <c r="B21" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137296854</v>
       </c>
       <c r="B22" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137296828</v>
       </c>
       <c r="B23" t="n">
-        <v>92084</v>
+        <v>92086</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137296825</v>
       </c>
       <c r="B24" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>137296847</v>
       </c>
       <c r="B28" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>137296858</v>
       </c>
       <c r="B29" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>137297071</v>
       </c>
       <c r="B30" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>137297074</v>
       </c>
       <c r="B31" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137297084</v>
       </c>
       <c r="B32" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>137297087</v>
       </c>
       <c r="B33" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137297088</v>
       </c>
       <c r="B34" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>137296821</v>
       </c>
       <c r="B128" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>137296826</v>
       </c>
       <c r="B129" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>137296827</v>
       </c>
       <c r="B130" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137297059</v>
       </c>
       <c r="B131" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>137297061</v>
       </c>
       <c r="B132" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>137297063</v>
       </c>
       <c r="B133" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>137297065</v>
       </c>
       <c r="B134" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>137297067</v>
       </c>
       <c r="B135" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137297068</v>
       </c>
       <c r="B136" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137297070</v>
       </c>
       <c r="B137" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>137297073</v>
       </c>
       <c r="B138" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>137297077</v>
       </c>
       <c r="B139" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>137297078</v>
       </c>
       <c r="B140" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>137297079</v>
       </c>
       <c r="B7" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137296849</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137296857</v>
       </c>
       <c r="B12" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137297080</v>
       </c>
       <c r="B13" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137296824</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137297076</v>
       </c>
       <c r="B17" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137296856</v>
       </c>
       <c r="B19" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137296859</v>
       </c>
       <c r="B20" t="n">
-        <v>92175</v>
+        <v>92180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137296853</v>
       </c>
       <c r="B21" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137296854</v>
       </c>
       <c r="B22" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137296828</v>
       </c>
       <c r="B23" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137296825</v>
       </c>
       <c r="B24" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>137296847</v>
       </c>
       <c r="B28" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>137296858</v>
       </c>
       <c r="B29" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>137297071</v>
       </c>
       <c r="B30" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>137297074</v>
       </c>
       <c r="B31" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137297084</v>
       </c>
       <c r="B32" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>137297087</v>
       </c>
       <c r="B33" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137297088</v>
       </c>
       <c r="B34" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>137296820</v>
       </c>
       <c r="B56" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>137296823</v>
       </c>
       <c r="B57" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>137296829</v>
       </c>
       <c r="B58" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>137296835</v>
       </c>
       <c r="B59" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>137296843</v>
       </c>
       <c r="B60" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>137296846</v>
       </c>
       <c r="B61" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>137296852</v>
       </c>
       <c r="B62" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>137297060</v>
       </c>
       <c r="B63" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>137297062</v>
       </c>
       <c r="B64" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137297064</v>
       </c>
       <c r="B65" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137297069</v>
       </c>
       <c r="B66" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>137297072</v>
       </c>
       <c r="B67" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>137297082</v>
       </c>
       <c r="B68" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>137297058</v>
       </c>
       <c r="B69" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>137296832</v>
       </c>
       <c r="B70" t="n">
-        <v>83490</v>
+        <v>83495</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>137296822</v>
       </c>
       <c r="B73" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>137296830</v>
       </c>
       <c r="B76" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137296839</v>
       </c>
       <c r="B77" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>137296844</v>
       </c>
       <c r="B78" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137296855</v>
       </c>
       <c r="B79" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>137297066</v>
       </c>
       <c r="B80" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>137296838</v>
       </c>
       <c r="B83" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137297056</v>
       </c>
       <c r="B95" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>137296841</v>
       </c>
       <c r="B101" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>137296831</v>
       </c>
       <c r="B102" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>137296833</v>
       </c>
       <c r="B103" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>137296836</v>
       </c>
       <c r="B104" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>137297075</v>
       </c>
       <c r="B105" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>137297085</v>
       </c>
       <c r="B106" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>137297086</v>
       </c>
       <c r="B107" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>137296842</v>
       </c>
       <c r="B108" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>137296848</v>
       </c>
       <c r="B113" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>137296851</v>
       </c>
       <c r="B115" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>137296821</v>
       </c>
       <c r="B128" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>137296826</v>
       </c>
       <c r="B129" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>137296827</v>
       </c>
       <c r="B130" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137297059</v>
       </c>
       <c r="B131" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>137297061</v>
       </c>
       <c r="B132" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>137297063</v>
       </c>
       <c r="B133" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>137297065</v>
       </c>
       <c r="B134" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>137297067</v>
       </c>
       <c r="B135" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137297068</v>
       </c>
       <c r="B136" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137297070</v>
       </c>
       <c r="B137" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>137297073</v>
       </c>
       <c r="B138" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>137297077</v>
       </c>
       <c r="B139" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>137297078</v>
       </c>
       <c r="B140" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>137296837</v>
       </c>
       <c r="B145" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>137296840</v>
       </c>
       <c r="B146" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>137297081</v>
       </c>
       <c r="B147" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>137297083</v>
       </c>
       <c r="B148" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>137297079</v>
       </c>
       <c r="B7" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137296849</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137296857</v>
       </c>
       <c r="B12" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137297080</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137296824</v>
       </c>
       <c r="B16" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137297076</v>
       </c>
       <c r="B17" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137296856</v>
       </c>
       <c r="B19" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137296859</v>
       </c>
       <c r="B20" t="n">
-        <v>92180</v>
+        <v>92192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137296853</v>
       </c>
       <c r="B21" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137296854</v>
       </c>
       <c r="B22" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137296828</v>
       </c>
       <c r="B23" t="n">
-        <v>92091</v>
+        <v>92103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137296825</v>
       </c>
       <c r="B24" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>137296847</v>
       </c>
       <c r="B28" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>137296858</v>
       </c>
       <c r="B29" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>137297071</v>
       </c>
       <c r="B30" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>137297074</v>
       </c>
       <c r="B31" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137297084</v>
       </c>
       <c r="B32" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>137297087</v>
       </c>
       <c r="B33" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137297088</v>
       </c>
       <c r="B34" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>137296820</v>
       </c>
       <c r="B56" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>137296823</v>
       </c>
       <c r="B57" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>137296829</v>
       </c>
       <c r="B58" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>137296835</v>
       </c>
       <c r="B59" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>137296843</v>
       </c>
       <c r="B60" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>137296846</v>
       </c>
       <c r="B61" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>137296852</v>
       </c>
       <c r="B62" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>137297060</v>
       </c>
       <c r="B63" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>137297062</v>
       </c>
       <c r="B64" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137297064</v>
       </c>
       <c r="B65" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137297069</v>
       </c>
       <c r="B66" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>137297072</v>
       </c>
       <c r="B67" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>137297082</v>
       </c>
       <c r="B68" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>137297058</v>
       </c>
       <c r="B69" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>137296832</v>
       </c>
       <c r="B70" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>137296822</v>
       </c>
       <c r="B73" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>137296830</v>
       </c>
       <c r="B76" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137296839</v>
       </c>
       <c r="B77" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>137296844</v>
       </c>
       <c r="B78" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137296855</v>
       </c>
       <c r="B79" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>137297066</v>
       </c>
       <c r="B80" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>137296838</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137297056</v>
       </c>
       <c r="B95" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>137296841</v>
       </c>
       <c r="B101" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>137296821</v>
       </c>
       <c r="B128" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>137296826</v>
       </c>
       <c r="B129" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>137296827</v>
       </c>
       <c r="B130" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137297059</v>
       </c>
       <c r="B131" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>137297061</v>
       </c>
       <c r="B132" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>137297063</v>
       </c>
       <c r="B133" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>137297065</v>
       </c>
       <c r="B134" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>137297067</v>
       </c>
       <c r="B135" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137297068</v>
       </c>
       <c r="B136" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137297070</v>
       </c>
       <c r="B137" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>137297073</v>
       </c>
       <c r="B138" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>137297077</v>
       </c>
       <c r="B139" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>137297078</v>
       </c>
       <c r="B140" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>137296837</v>
       </c>
       <c r="B145" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>137296840</v>
       </c>
       <c r="B146" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>137297081</v>
       </c>
       <c r="B147" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>137297083</v>
       </c>
       <c r="B148" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>137297079</v>
       </c>
       <c r="B7" t="n">
-        <v>92427</v>
+        <v>92428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137296849</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137296857</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137297080</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137296824</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137297076</v>
       </c>
       <c r="B17" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137296856</v>
       </c>
       <c r="B19" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137296859</v>
       </c>
       <c r="B20" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137296853</v>
       </c>
       <c r="B21" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137296854</v>
       </c>
       <c r="B22" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137296828</v>
       </c>
       <c r="B23" t="n">
-        <v>92103</v>
+        <v>92104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137296825</v>
       </c>
       <c r="B24" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>137296847</v>
       </c>
       <c r="B28" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>137296858</v>
       </c>
       <c r="B29" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>137297071</v>
       </c>
       <c r="B30" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>137297074</v>
       </c>
       <c r="B31" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137297084</v>
       </c>
       <c r="B32" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>137297087</v>
       </c>
       <c r="B33" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137297088</v>
       </c>
       <c r="B34" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>137296820</v>
       </c>
       <c r="B56" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>137296823</v>
       </c>
       <c r="B57" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>137296829</v>
       </c>
       <c r="B58" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>137296835</v>
       </c>
       <c r="B59" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>137296843</v>
       </c>
       <c r="B60" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>137296846</v>
       </c>
       <c r="B61" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>137296852</v>
       </c>
       <c r="B62" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>137297060</v>
       </c>
       <c r="B63" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>137297062</v>
       </c>
       <c r="B64" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137297064</v>
       </c>
       <c r="B65" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137297069</v>
       </c>
       <c r="B66" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>137297072</v>
       </c>
       <c r="B67" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>137297082</v>
       </c>
       <c r="B68" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>137297058</v>
       </c>
       <c r="B69" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>137296832</v>
       </c>
       <c r="B70" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>137296822</v>
       </c>
       <c r="B73" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>137296830</v>
       </c>
       <c r="B76" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137296839</v>
       </c>
       <c r="B77" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>137296844</v>
       </c>
       <c r="B78" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137296855</v>
       </c>
       <c r="B79" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>137297066</v>
       </c>
       <c r="B80" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>137296838</v>
       </c>
       <c r="B83" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137297056</v>
       </c>
       <c r="B95" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>137296841</v>
       </c>
       <c r="B101" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>137296821</v>
       </c>
       <c r="B128" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>137296826</v>
       </c>
       <c r="B129" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>137296827</v>
       </c>
       <c r="B130" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137297059</v>
       </c>
       <c r="B131" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>137297061</v>
       </c>
       <c r="B132" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>137297063</v>
       </c>
       <c r="B133" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>137297065</v>
       </c>
       <c r="B134" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>137297067</v>
       </c>
       <c r="B135" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137297068</v>
       </c>
       <c r="B136" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137297070</v>
       </c>
       <c r="B137" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>137297073</v>
       </c>
       <c r="B138" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>137297077</v>
       </c>
       <c r="B139" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>137297078</v>
       </c>
       <c r="B140" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>137296837</v>
       </c>
       <c r="B145" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>137296840</v>
       </c>
       <c r="B146" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>137297081</v>
       </c>
       <c r="B147" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>137297083</v>
       </c>
       <c r="B148" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>137297079</v>
       </c>
       <c r="B7" t="n">
-        <v>92428</v>
+        <v>92431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137296849</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137296857</v>
       </c>
       <c r="B12" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137297080</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137296824</v>
       </c>
       <c r="B16" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137297076</v>
       </c>
       <c r="B17" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137296856</v>
       </c>
       <c r="B19" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137296859</v>
       </c>
       <c r="B20" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137296853</v>
       </c>
       <c r="B21" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137296854</v>
       </c>
       <c r="B22" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137296828</v>
       </c>
       <c r="B23" t="n">
-        <v>92104</v>
+        <v>92107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137296825</v>
       </c>
       <c r="B24" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>137296847</v>
       </c>
       <c r="B28" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>137296858</v>
       </c>
       <c r="B29" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>137297071</v>
       </c>
       <c r="B30" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>137297074</v>
       </c>
       <c r="B31" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137297084</v>
       </c>
       <c r="B32" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>137297087</v>
       </c>
       <c r="B33" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137297088</v>
       </c>
       <c r="B34" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>137296820</v>
       </c>
       <c r="B56" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>137296823</v>
       </c>
       <c r="B57" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>137296829</v>
       </c>
       <c r="B58" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>137296835</v>
       </c>
       <c r="B59" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>137296843</v>
       </c>
       <c r="B60" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>137296846</v>
       </c>
       <c r="B61" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>137296852</v>
       </c>
       <c r="B62" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>137297060</v>
       </c>
       <c r="B63" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>137297062</v>
       </c>
       <c r="B64" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137297064</v>
       </c>
       <c r="B65" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137297069</v>
       </c>
       <c r="B66" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>137297072</v>
       </c>
       <c r="B67" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>137297082</v>
       </c>
       <c r="B68" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>137297058</v>
       </c>
       <c r="B69" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>137296832</v>
       </c>
       <c r="B70" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>137296822</v>
       </c>
       <c r="B73" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>137296830</v>
       </c>
       <c r="B76" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137296839</v>
       </c>
       <c r="B77" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>137296844</v>
       </c>
       <c r="B78" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137296855</v>
       </c>
       <c r="B79" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>137297066</v>
       </c>
       <c r="B80" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>137296838</v>
       </c>
       <c r="B83" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137297056</v>
       </c>
       <c r="B95" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>137296841</v>
       </c>
       <c r="B101" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>137296821</v>
       </c>
       <c r="B128" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>137296826</v>
       </c>
       <c r="B129" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>137296827</v>
       </c>
       <c r="B130" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137297059</v>
       </c>
       <c r="B131" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>137297061</v>
       </c>
       <c r="B132" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>137297063</v>
       </c>
       <c r="B133" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>137297065</v>
       </c>
       <c r="B134" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>137297067</v>
       </c>
       <c r="B135" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137297068</v>
       </c>
       <c r="B136" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137297070</v>
       </c>
       <c r="B137" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>137297073</v>
       </c>
       <c r="B138" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>137297077</v>
       </c>
       <c r="B139" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>137297078</v>
       </c>
       <c r="B140" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>137296837</v>
       </c>
       <c r="B145" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>137296840</v>
       </c>
       <c r="B146" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>137297081</v>
       </c>
       <c r="B147" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>137297083</v>
       </c>
       <c r="B148" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>137297079</v>
       </c>
       <c r="B7" t="n">
-        <v>92431</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137296849</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137296857</v>
       </c>
       <c r="B12" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137297080</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137296824</v>
       </c>
       <c r="B16" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137297076</v>
       </c>
       <c r="B17" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137296856</v>
       </c>
       <c r="B19" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137296859</v>
       </c>
       <c r="B20" t="n">
-        <v>92196</v>
+        <v>92200</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137296853</v>
       </c>
       <c r="B21" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137296854</v>
       </c>
       <c r="B22" t="n">
-        <v>92238</v>
+        <v>92242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137296828</v>
       </c>
       <c r="B23" t="n">
-        <v>92107</v>
+        <v>92111</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137296825</v>
       </c>
       <c r="B24" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>137296847</v>
       </c>
       <c r="B28" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>137296858</v>
       </c>
       <c r="B29" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>137297071</v>
       </c>
       <c r="B30" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>137297074</v>
       </c>
       <c r="B31" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137297084</v>
       </c>
       <c r="B32" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>137297087</v>
       </c>
       <c r="B33" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>137297088</v>
       </c>
       <c r="B34" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>137296820</v>
       </c>
       <c r="B56" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>137296823</v>
       </c>
       <c r="B57" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>137296829</v>
       </c>
       <c r="B58" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>137296835</v>
       </c>
       <c r="B59" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>137296843</v>
       </c>
       <c r="B60" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>137296846</v>
       </c>
       <c r="B61" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>137296852</v>
       </c>
       <c r="B62" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>137297060</v>
       </c>
       <c r="B63" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>137297062</v>
       </c>
       <c r="B64" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137297064</v>
       </c>
       <c r="B65" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137297069</v>
       </c>
       <c r="B66" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>137297072</v>
       </c>
       <c r="B67" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>137297082</v>
       </c>
       <c r="B68" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>137297058</v>
       </c>
       <c r="B69" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>137296832</v>
       </c>
       <c r="B70" t="n">
-        <v>83509</v>
+        <v>83513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>137296822</v>
       </c>
       <c r="B73" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>137296830</v>
       </c>
       <c r="B76" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137296839</v>
       </c>
       <c r="B77" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>137296844</v>
       </c>
       <c r="B78" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137296855</v>
       </c>
       <c r="B79" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>137297066</v>
       </c>
       <c r="B80" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>137296838</v>
       </c>
       <c r="B83" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137297056</v>
       </c>
       <c r="B95" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>137296841</v>
       </c>
       <c r="B101" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>137296831</v>
       </c>
       <c r="B102" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>137296833</v>
       </c>
       <c r="B103" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>137296836</v>
       </c>
       <c r="B104" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>137297075</v>
       </c>
       <c r="B105" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>137297085</v>
       </c>
       <c r="B106" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>137297086</v>
       </c>
       <c r="B107" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>137296842</v>
       </c>
       <c r="B108" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>137296848</v>
       </c>
       <c r="B113" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>137296851</v>
       </c>
       <c r="B115" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>137296821</v>
       </c>
       <c r="B128" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>137296826</v>
       </c>
       <c r="B129" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>137296827</v>
       </c>
       <c r="B130" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137297059</v>
       </c>
       <c r="B131" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>137297061</v>
       </c>
       <c r="B132" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>137297063</v>
       </c>
       <c r="B133" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>137297065</v>
       </c>
       <c r="B134" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>137297067</v>
       </c>
       <c r="B135" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>137297068</v>
       </c>
       <c r="B136" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137297070</v>
       </c>
       <c r="B137" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>137297073</v>
       </c>
       <c r="B138" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>137297077</v>
       </c>
       <c r="B139" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>137297078</v>
       </c>
       <c r="B140" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>137296837</v>
       </c>
       <c r="B145" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>137296840</v>
       </c>
       <c r="B146" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>137297081</v>
       </c>
       <c r="B147" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>137297083</v>
       </c>
       <c r="B148" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
